--- a/results/job_matches_2026-06-08.xlsx
+++ b/results/job_matches_2026-06-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5b9e1941fe0d4ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Analytics Engineer</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Casey's</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Ankeny, IA, US USA</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
         <v>11.8</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1fdc7b0acc6f95</t>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92370ed8cefd2963</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c72aec67782f8030</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-08.xlsx
+++ b/results/job_matches_2026-06-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,15 +556,85 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=953100d783ca43ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72b083a5bbeb1232</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c72aec67782f8030</t>
         </is>

--- a/results/job_matches_2026-06-08.xlsx
+++ b/results/job_matches_2026-06-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineering Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.9</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,147 +496,672 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b9e1941fe0d4ca</t>
+          <t>https://www.indeed.com/viewjob?jk=8d42d7af82b11801</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Techno Functional Solutions Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92370ed8cefd2963</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6462d7517c54df</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Data/ML Engineer (AWS)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=953100d783ca43ac</t>
+          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Engineer, Engineering Services</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b083a5bbeb1232</t>
+          <t>https://www.indeed.com/viewjob?jk=e247743b45089523</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Sr. Java Developer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Symplore Inc</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Texas City, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3af98f3363aa097a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5b9e1941fe0d4ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Oracle, ETL, CI/CD, Jenkins, Maven</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f72dbc4b18bcb75</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Smithfield, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Oracle, ETL, CI/CD, Jenkins, Maven</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86d4421552e0b63d</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MOEV Inc.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, MLOps</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33470d4830492356</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Software Engineering Senior Advisor- Hybrid</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ceca754c6b6fbfd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Blockchain Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=678a055b3ce18049</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Casey's</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ankeny, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92370ed8cefd2963</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Metronet</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8988ab1d912fc2fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Platforms &amp; Monetization</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Wowza Media Systems</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, RDS, MySQL, Data Modeling, ETL, REST API integration, Terraform</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa5b3c703b2170b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=953100d783ca43ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72b083a5bbeb1232</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Seattle, WA, US USA</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D18" t="n">
         <v>10.4</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c72aec67782f8030</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Everforth ECS</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ec915a33af5dd7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sales Operations - Business Intelligence Engineer II</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Milwaukee Tool</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82347e7049db91bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, AI Solutions Hub (AISH)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Northeastern University</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ceb267d00866d172</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-08.xlsx
+++ b/results/job_matches_2026-06-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d42d7af82b11801</t>
+          <t>https://www.indeed.com/viewjob?jk=3b55889f7ea9b40e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Techno Functional Solutions Architect</t>
+          <t>Software Engineering Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6462d7517c54df</t>
+          <t>https://www.indeed.com/viewjob?jk=8d42d7af82b11801</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data/ML Engineer (AWS)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, API Gateway, RDS, Azure</t>
+          <t>AWS, Lambda, Kinesis, S3, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
+          <t>https://www.indeed.com/viewjob?jk=882f952f94db3f29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Engineer, Engineering Services</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e247743b45089523</t>
+          <t>https://www.indeed.com/viewjob?jk=877524bbcd4e4f56</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Java Developer</t>
+          <t>Techno Functional Solutions Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Symplore Inc</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af98f3363aa097a</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6462d7517c54df</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>System Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Data Science Software LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b9e1941fe0d4ca</t>
+          <t>https://www.indeed.com/viewjob?jk=fea9058a7f90d508</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data/ML Engineer (AWS)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Oracle, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f72dbc4b18bcb75</t>
+          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - PGIM Technology</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Oracle, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d4421552e0b63d</t>
+          <t>https://www.indeed.com/viewjob?jk=42ddb3e15556877d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Java Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MOEV Inc.</t>
+          <t>Symplore Inc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33470d4830492356</t>
+          <t>https://www.indeed.com/viewjob?jk=3af98f3363aa097a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor- Hybrid</t>
+          <t>Senior Engineer, Engineering Services</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceca754c6b6fbfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=e247743b45089523</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Blockchain Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,15 +828,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678a055b3ce18049</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b9e1941fe0d4ca</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Oracle, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92370ed8cefd2963</t>
+          <t>https://www.indeed.com/viewjob?jk=2f72dbc4b18bcb75</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Metronet</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Oracle, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8988ab1d912fc2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=86d4421552e0b63d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platforms &amp; Monetization</t>
+          <t>Senior Software Engineer - Middleware &amp; Integration</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wowza Media Systems</t>
+          <t>STAND TOGETHER</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, MySQL, Data Modeling, ETL, REST API integration, Terraform</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5b3c703b2170b9</t>
+          <t>https://www.indeed.com/viewjob?jk=d777bc5639f13b8d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>MOEV Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=953100d783ca43ac</t>
+          <t>https://www.indeed.com/viewjob?jk=33470d4830492356</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Sr Software Engineer - AWS full stack</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b083a5bbeb1232</t>
+          <t>https://www.indeed.com/viewjob?jk=88642e48dab563ae</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+          <t>Data Engineer – Python + React (Healthcare Domain)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Nova Web Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72aec67782f8030</t>
+          <t>https://www.indeed.com/viewjob?jk=ff5c44492f4137d0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineering Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec915a33af5dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ab95bf144a98568</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sales Operations - Business Intelligence Engineer II</t>
+          <t>Software Engineering Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI, Tableau</t>
+          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,40 +1126,600 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82347e7049db91bd</t>
+          <t>https://www.indeed.com/viewjob?jk=ceca754c6b6fbfd5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Senior Blockchain Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=678a055b3ce18049</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Casey's</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ankeny, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92370ed8cefd2963</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Engineer, Go to Market (Remote)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27f893425f230116</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Metronet</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8988ab1d912fc2fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Offchain Labs</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, CodeBuild, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a00c080490fe5a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Kubernetes / XNAT Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>XNAT Works Inc.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Hive, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86cc83af06965162</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Platforms &amp; Monetization</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Wowza Media Systems</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, RDS, MySQL, Data Modeling, ETL, REST API integration, Terraform</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa5b3c703b2170b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=953100d783ca43ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72b083a5bbeb1232</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>The Carlyle Group</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35918117efc7ec73</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist-Manufacturing</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50ab1973f17e0989</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Position 616-05</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Citco</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2ccb465cac7664e</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c72aec67782f8030</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Everforth ECS</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ec915a33af5dd7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Engineer, Payments Checkouts - Publishing Platform</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Riot Games</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64dd743e4a8a5177</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sales Operations - Business Intelligence Engineer II</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Milwaukee Tool</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82347e7049db91bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Machine Learning Engineer, AI Solutions Hub (AISH)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Northeastern University</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Portland, ME, US USA</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D37" t="n">
         <v>10.4</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ceb267d00866d172</t>
         </is>

--- a/results/job_matches_2026-06-08.xlsx
+++ b/results/job_matches_2026-06-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,20 +543,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, API Gateway, IAM, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882f952f94db3f29</t>
+          <t>https://www.indeed.com/viewjob?jk=2da5893cfc35a86b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, Lambda, Kinesis, S3, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877524bbcd4e4f56</t>
+          <t>https://www.indeed.com/viewjob?jk=882f952f94db3f29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Techno Functional Solutions Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6462d7517c54df</t>
+          <t>https://www.indeed.com/viewjob?jk=877524bbcd4e4f56</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>System Architect</t>
+          <t>Techno Functional Solutions Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Data Science Software LLC</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea9058a7f90d508</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6462d7517c54df</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data/ML Engineer (AWS)</t>
+          <t>System Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>Data Science Software LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, API Gateway, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
+          <t>https://www.indeed.com/viewjob?jk=fea9058a7f90d508</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PGIM Technology</t>
+          <t>Distinguished Software Engineer (Big Data &amp; AI)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ddb3e15556877d</t>
+          <t>https://www.indeed.com/viewjob?jk=a981ef29c01bf602</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Java Developer</t>
+          <t>Senior Data/ML Engineer (AWS)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Symplore Inc</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af98f3363aa097a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer, Engineering Services</t>
+          <t>Senior Data Engineer - PGIM Technology (Hybrid - Newark, NJ)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>PGIM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e247743b45089523</t>
+          <t>https://www.indeed.com/viewjob?jk=b7feca5e666659d5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - PGIM Technology</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b9e1941fe0d4ca</t>
+          <t>https://www.indeed.com/viewjob?jk=42ddb3e15556877d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Analytics</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Lovevery</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Oracle, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f72dbc4b18bcb75</t>
+          <t>https://www.indeed.com/viewjob?jk=b019f71f6d426d97</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>ProcyonIT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Oracle, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d4421552e0b63d</t>
+          <t>https://www.indeed.com/viewjob?jk=6834afba60249fdb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Middleware &amp; Integration</t>
+          <t>Senior Engineer, Investment Technology</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>STAND TOGETHER</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d777bc5639f13b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=e247743b45089523</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MOEV Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, MLOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33470d4830492356</t>
+          <t>https://www.indeed.com/viewjob?jk=5232892f9a4a9b08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AWS full stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88642e48dab563ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b9e1941fe0d4ca</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer – Python + React (Healthcare Domain)</t>
+          <t>Senior Software Engineer - Middleware &amp; Integration</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nova Web Technologies</t>
+          <t>STAND TOGETHER</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff5c44492f4137d0</t>
+          <t>https://www.indeed.com/viewjob?jk=d777bc5639f13b8d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor- Hybrid</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>MOEV Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab95bf144a98568</t>
+          <t>https://www.indeed.com/viewjob?jk=33470d4830492356</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor- Hybrid</t>
+          <t>Senior BI Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Soleo Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceca754c6b6fbfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=dedc6497a9161a47</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Blockchain Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678a055b3ce18049</t>
+          <t>https://www.indeed.com/viewjob?jk=33d845a6e90fbede</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Software Engineer - AWS full stack</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92370ed8cefd2963</t>
+          <t>https://www.indeed.com/viewjob?jk=88642e48dab563ae</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f893425f230116</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd5208875d3c1b2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer – Python + React (Healthcare Domain)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Metronet</t>
+          <t>Nova Web Technologies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8988ab1d912fc2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ff5c44492f4137d0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Offchain Labs</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, CodeBuild, Terraform, Kubernetes</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a00c080490fe5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2c3719c3e2ec42</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kubernetes / XNAT Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>XNAT Works Inc.</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hive, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86cc83af06965162</t>
+          <t>https://www.indeed.com/viewjob?jk=55da546db249541e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platforms &amp; Monetization</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wowza Media Systems</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, MySQL, Data Modeling, ETL, REST API integration, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,172 +1371,172 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5b3c703b2170b9</t>
+          <t>https://www.indeed.com/viewjob?jk=cde05fe8d78b7bea</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer (.NET )</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=953100d783ca43ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a8fae101fea70214</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineering Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b083a5bbeb1232</t>
+          <t>https://www.indeed.com/viewjob?jk=1ab95bf144a98568</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Software Engineering Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35918117efc7ec73</t>
+          <t>https://www.indeed.com/viewjob?jk=ceca754c6b6fbfd5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist-Manufacturing</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50ab1973f17e0989</t>
+          <t>https://www.indeed.com/viewjob?jk=92370ed8cefd2963</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Position 616-05</t>
+          <t>Senior Blockchain Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Citco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ccb465cac7664e</t>
+          <t>https://www.indeed.com/viewjob?jk=678a055b3ce18049</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72aec67782f8030</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9a027a38e2401</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec915a33af5dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=27f893425f230116</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer, Payments Checkouts - Publishing Platform</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Riot Games</t>
+          <t>Metronet</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dd743e4a8a5177</t>
+          <t>https://www.indeed.com/viewjob?jk=8988ab1d912fc2fc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sales Operations - Business Intelligence Engineer II</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Offchain Labs</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, CodeBuild, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82347e7049db91bd</t>
+          <t>https://www.indeed.com/viewjob?jk=8a00c080490fe5a6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, AI Solutions Hub (AISH)</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Hive, Spark, PySpark, Scala, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,497 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb267d00866d172</t>
+          <t>https://www.indeed.com/viewjob?jk=409022a27d0ec067</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Junior Data Engineer (Faculty Specialist)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>University of Maryland University College</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>College Park, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Hadoop, Hive, Spark, SQL Server, PostgreSQL, Cassandra, ETL, Git</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aaedc5d1808c1ed5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Platforms &amp; Monetization</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Wowza Media Systems</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, RDS, MySQL, Data Modeling, ETL, REST API integration, Terraform</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa5b3c703b2170b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=953100d783ca43ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72b083a5bbeb1232</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>The Carlyle Group</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35918117efc7ec73</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sr. Java/AWS Software Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Client Resources, Inc.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Maven</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8732c30c0b6792f</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sr Software Quality Engineer (Exp w/ AI Techniques)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Aspen Technology</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Bedford, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f74bc4c0820330e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist-Manufacturing</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50ab1973f17e0989</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Software Engineer, Payments Checkouts - Publishing Platform</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Riot Games</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64dd743e4a8a5177</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Data Architect 3 (Data Analyst 3)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>University of Connecticut</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Storrs, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, SQL Server, ETL, Pentaho, Power BI, Airflow, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b2f300a70f64192</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Position 616-05</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Citco</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2ccb465cac7664e</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c72aec67782f8030</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Sales Operations - Business Intelligence Engineer II</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Milwaukee Tool</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82347e7049db91bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Everforth ECS</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ec915a33af5dd7f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-08.xlsx
+++ b/results/job_matches_2026-06-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2da5893cfc35a86b</t>
+          <t>https://www.indeed.com/viewjob?jk=d18ea85c2c928c35</t>
         </is>
       </c>
     </row>
@@ -578,20 +578,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, API Gateway, IAM, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882f952f94db3f29</t>
+          <t>https://www.indeed.com/viewjob?jk=2da5893cfc35a86b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, RDS, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877524bbcd4e4f56</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2b721d35d7a5a7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Techno Functional Solutions Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6462d7517c54df</t>
+          <t>https://www.indeed.com/viewjob?jk=882f952f94db3f29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>System Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Data Science Software LLC</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea9058a7f90d508</t>
+          <t>https://www.indeed.com/viewjob?jk=877524bbcd4e4f56</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Distinguished Software Engineer (Big Data &amp; AI)</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a981ef29c01bf602</t>
+          <t>https://www.indeed.com/viewjob?jk=7cd0ed9ff6e64aa7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data/ML Engineer (AWS)</t>
+          <t>System Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>Data Science Software LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, API Gateway, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
+          <t>https://www.indeed.com/viewjob?jk=fea9058a7f90d508</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PGIM Technology (Hybrid - Newark, NJ)</t>
+          <t>Distinguished Software Engineer (Big Data &amp; AI)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PGIM</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7feca5e666659d5</t>
+          <t>https://www.indeed.com/viewjob?jk=a981ef29c01bf602</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PGIM Technology</t>
+          <t>Senior Data/ML Engineer (AWS)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ddb3e15556877d</t>
+          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Analytics</t>
+          <t>Senior Data Engineer - PGIM Technology (Hybrid - Newark, NJ)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lovevery</t>
+          <t>PGIM</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b019f71f6d426d97</t>
+          <t>https://www.indeed.com/viewjob?jk=b7feca5e666659d5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Senior Data Engineer - PGIM Technology</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ProcyonIT</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6834afba60249fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=42ddb3e15556877d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Engineer, Investment Technology</t>
+          <t>Senior Data Engineer, Analytics</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Lovevery</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e247743b45089523</t>
+          <t>https://www.indeed.com/viewjob?jk=b019f71f6d426d97</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ProcyonIT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5232892f9a4a9b08</t>
+          <t>https://www.indeed.com/viewjob?jk=6834afba60249fdb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Investment Technology</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b9e1941fe0d4ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e247743b45089523</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Middleware &amp; Integration</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>STAND TOGETHER</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d777bc5639f13b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=10ead8343cec4879</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MOEV Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33470d4830492356</t>
+          <t>https://www.indeed.com/viewjob?jk=162c2ab9f292809c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior BI Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Soleo Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedc6497a9161a47</t>
+          <t>https://www.indeed.com/viewjob?jk=d7be54a20fbf4431</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DTN</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d845a6e90fbede</t>
+          <t>https://www.indeed.com/viewjob?jk=6773c1c434a7ae57</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AWS full stack</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88642e48dab563ae</t>
+          <t>https://www.indeed.com/viewjob?jk=5232892f9a4a9b08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd5208875d3c1b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b9e1941fe0d4ca</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer – Python + React (Healthcare Domain)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nova Web Technologies</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff5c44492f4137d0</t>
+          <t>https://www.indeed.com/viewjob?jk=8d135475bf2adc12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer (Advanced Threat Protection)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>MOEV Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2c3719c3e2ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=33470d4830492356</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior BI Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Soleo Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55da546db249541e</t>
+          <t>https://www.indeed.com/viewjob?jk=dedc6497a9161a47</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde05fe8d78b7bea</t>
+          <t>https://www.indeed.com/viewjob?jk=33d845a6e90fbede</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (.NET )</t>
+          <t>Sr Software Engineer - AWS full stack</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8fae101fea70214</t>
+          <t>https://www.indeed.com/viewjob?jk=88642e48dab563ae</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor- Hybrid</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab95bf144a98568</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd5208875d3c1b2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor- Hybrid</t>
+          <t>Data Engineer – Python + React (Healthcare Domain)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Nova Web Technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceca754c6b6fbfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=ff5c44492f4137d0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Azure Engineer (Associate)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92370ed8cefd2963</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbe236b626e4a53</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Blockchain Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678a055b3ce18049</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2c3719c3e2ec42</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Rise Collective</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9a027a38e2401</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3b252b91a197e5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>Software Engineering Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f893425f230116</t>
+          <t>https://www.indeed.com/viewjob?jk=1ab95bf144a98568</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineering Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Metronet</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8988ab1d912fc2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ceca754c6b6fbfd5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer (.NET )</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Offchain Labs</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, CodeBuild, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a00c080490fe5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a8fae101fea70214</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Hive, Spark, PySpark, Scala, ETL, ELT, Terraform</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=409022a27d0ec067</t>
+          <t>https://www.indeed.com/viewjob?jk=92370ed8cefd2963</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Junior Data Engineer (Faculty Specialist)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Spark, SQL Server, PostgreSQL, Cassandra, ETL, Git</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaedc5d1808c1ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=55da546db249541e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platforms &amp; Monetization</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wowza Media Systems</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, MySQL, Data Modeling, ETL, REST API integration, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,137 +1791,137 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5b3c703b2170b9</t>
+          <t>https://www.indeed.com/viewjob?jk=cde05fe8d78b7bea</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Blockchain Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=953100d783ca43ac</t>
+          <t>https://www.indeed.com/viewjob?jk=678a055b3ce18049</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b083a5bbeb1232</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9a027a38e2401</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35918117efc7ec73</t>
+          <t>https://www.indeed.com/viewjob?jk=27f893425f230116</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Java/AWS Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>Metronet</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Maven</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8732c30c0b6792f</t>
+          <t>https://www.indeed.com/viewjob?jk=8988ab1d912fc2fc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Software Quality Engineer (Exp w/ AI Techniques)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Aspen Technology</t>
+          <t>Offchain Labs</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bedford, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, CodeBuild, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f74bc4c0820330e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a00c080490fe5a6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist-Manufacturing</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Hive, Spark, PySpark, Scala, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50ab1973f17e0989</t>
+          <t>https://www.indeed.com/viewjob?jk=409022a27d0ec067</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer, Payments Checkouts - Publishing Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Riot Games</t>
+          <t>Snooze an AM Eatery</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dd743e4a8a5177</t>
+          <t>https://www.indeed.com/viewjob?jk=65eaed35b3d68901</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Architect 3 (Data Analyst 3)</t>
+          <t>Junior Data Engineer (Faculty Specialist)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Storrs, CT, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, ETL, Pentaho, Power BI, Airflow, Python, SQL</t>
+          <t>AWS, GCP, Hadoop, Hive, Spark, SQL Server, PostgreSQL, Cassandra, ETL, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b2f300a70f64192</t>
+          <t>https://www.indeed.com/viewjob?jk=aaedc5d1808c1ed5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Position 616-05</t>
+          <t>Senior Software Engineer, Data Platforms &amp; Monetization</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Citco</t>
+          <t>Wowza Media Systems</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+          <t>AWS, Glue, Lambda, S3, RDS, MySQL, Data Modeling, ETL, REST API integration, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ccb465cac7664e</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5b3c703b2170b9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72aec67782f8030</t>
+          <t>https://www.indeed.com/viewjob?jk=953100d783ca43ac</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sales Operations - Business Intelligence Engineer II</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82347e7049db91bd</t>
+          <t>https://www.indeed.com/viewjob?jk=72b083a5bbeb1232</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,297 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35918117efc7ec73</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Data Architect 3 (Data Analyst 3)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>University of Connecticut</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Storrs, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, SQL Server, ETL, Pentaho, Power BI, Airflow, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b2f300a70f64192</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sr Software Quality Engineer (Exp w/ AI Techniques)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Aspen Technology</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Bedford, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f74bc4c0820330e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist-Manufacturing</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50ab1973f17e0989</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Position 616-05</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Citco</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2ccb465cac7664e</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sr. Java/AWS Software Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Client Resources, Inc.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Maven</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8732c30c0b6792f</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Sales Operations - Business Intelligence Engineer II</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Milwaukee Tool</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82347e7049db91bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Everforth ECS</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2ec915a33af5dd7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c72aec67782f8030</t>
         </is>
       </c>
     </row>
